--- a/agriculture 52.xlsx
+++ b/agriculture 52.xlsx
@@ -223,7 +223,7 @@
     <t xml:space="preserve">2020-21</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- </t>
+    <t xml:space="preserve">Unit:- Percentage(%)</t>
   </si>
   <si>
     <t xml:space="preserve">Source:  EPWRF (Economic &amp; Political Weekly  Reasearch Foundation) 1964-2021</t>
@@ -236,6 +236,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Source Description: </t>
     </r>
@@ -245,6 +246,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">1966-67 to 2007-08: Plantation Crops: Arecanut:-&gt; Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
     </r>
@@ -264,7 +266,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -291,6 +293,7 @@
       <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -302,21 +305,10 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -375,7 +367,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -396,15 +388,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -426,7 +422,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M1048576"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="0" width="11.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11.62"/>
@@ -2413,89 +2409,89 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="3" t="s">
+      <c r="A56" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
-      <c r="J56" s="3"/>
-      <c r="K56" s="3"/>
-      <c r="L56" s="3"/>
-      <c r="M56" s="3"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="5"/>
+      <c r="J56" s="5"/>
+      <c r="K56" s="5"/>
+      <c r="L56" s="5"/>
+      <c r="M56" s="5"/>
     </row>
     <row r="57" customFormat="false" ht="37.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="5" t="s">
+      <c r="A57" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
-      <c r="H57" s="5"/>
-      <c r="I57" s="5"/>
-      <c r="J57" s="5"/>
-      <c r="K57" s="5"/>
-      <c r="L57" s="5"/>
-      <c r="M57" s="5"/>
+      <c r="B57" s="6"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="6"/>
+      <c r="K57" s="6"/>
+      <c r="L57" s="6"/>
+      <c r="M57" s="6"/>
     </row>
     <row r="58" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B58" s="6"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6"/>
-      <c r="J58" s="6"/>
-      <c r="K58" s="6"/>
-      <c r="L58" s="6"/>
-      <c r="M58" s="6"/>
+      <c r="B58" s="7"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="7"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="7"/>
+      <c r="J58" s="7"/>
+      <c r="K58" s="7"/>
+      <c r="L58" s="7"/>
+      <c r="M58" s="7"/>
     </row>
     <row r="59" customFormat="false" ht="83.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="7" t="s">
+      <c r="A59" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B59" s="7"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-      <c r="G59" s="7"/>
-      <c r="H59" s="7"/>
-      <c r="I59" s="7"/>
-      <c r="J59" s="7"/>
-      <c r="K59" s="7"/>
-      <c r="L59" s="7"/>
-      <c r="M59" s="7"/>
+      <c r="B59" s="8"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="8"/>
+      <c r="I59" s="8"/>
+      <c r="J59" s="8"/>
+      <c r="K59" s="8"/>
+      <c r="L59" s="8"/>
+      <c r="M59" s="8"/>
     </row>
     <row r="60" customFormat="false" ht="49.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="7" t="s">
+      <c r="A60" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B60" s="7"/>
-      <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
-      <c r="G60" s="7"/>
-      <c r="H60" s="7"/>
-      <c r="I60" s="7"/>
-      <c r="J60" s="7"/>
-      <c r="K60" s="7"/>
-      <c r="L60" s="7"/>
-      <c r="M60" s="7"/>
+      <c r="B60" s="8"/>
+      <c r="C60" s="8"/>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="8"/>
+      <c r="G60" s="8"/>
+      <c r="H60" s="8"/>
+      <c r="I60" s="8"/>
+      <c r="J60" s="8"/>
+      <c r="K60" s="8"/>
+      <c r="L60" s="8"/>
+      <c r="M60" s="8"/>
     </row>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/agriculture 52.xlsx
+++ b/agriculture 52.xlsx
@@ -223,7 +223,7 @@
     <t xml:space="preserve">2020-21</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- Percentage(%)</t>
+    <t xml:space="preserve">Unit:- Percentage (%)</t>
   </si>
   <si>
     <t xml:space="preserve">Source:  EPWRF (Economic &amp; Political Weekly  Reasearch Foundation) 1964-2021</t>
@@ -422,7 +422,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M1048576"/>
-  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.82421875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="0" width="11.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11.62"/>
